--- a/00_LATEST_PRESENTED_DECK_AND_DELIVERABLES/ORAN_Fault_Detectability_v2026-10-05.xlsx
+++ b/00_LATEST_PRESENTED_DECK_AND_DELIVERABLES/ORAN_Fault_Detectability_v2026-10-05.xlsx
@@ -1134,7 +1134,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -2406,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2586,10 +2586,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>REC</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Measured 5 Oct 2026 in the recovery-loop evaluation (03_RECOVERY_LOOP_S-PLANE, control arm, replicates 13-17): pmc -d 24 PARENT_DATA_SET of RU1/RU2 every 0.5 s, same injection mechanisms as the campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>B6M</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Measured in this project: two-laptop crystal comparison, 2 Oct 2026, outputs/B6_two_machine_2026-10-02/run2/DRIFT_REPORT_run2.md (run 2 ESTABLISHED, +21.013 ppm [20.623, 21.403]; run 1 NOT ESTABLISHED, +20.161 ppm; the 0.852 ppm run-to-run difference exceeds either CI). Consumer laptop crystals against an NTP reference - not telecom-class oscillators</t>
         </is>
